--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.09680217405627</v>
+        <v>9.115730353284144</v>
       </c>
       <c r="D2" t="n">
-        <v>56.0978500811223</v>
+        <v>9.115900638182374</v>
       </c>
       <c r="E2" t="n">
-        <v>33.88856900210827</v>
+        <v>5.506892462842593</v>
       </c>
       <c r="F2" t="n">
-        <v>20.66779025293812</v>
+        <v>3.358515916102444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.97186496795612</v>
+        <v>6.98292805729287</v>
       </c>
       <c r="D3" t="n">
-        <v>61.21322840568962</v>
+        <v>9.947149615924564</v>
       </c>
       <c r="E3" t="n">
-        <v>33.88856900210827</v>
+        <v>5.506892462842593</v>
       </c>
       <c r="F3" t="n">
-        <v>20.66779025293812</v>
+        <v>3.358515916102444</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.67778457193248</v>
+        <v>1.897639992939029</v>
       </c>
       <c r="D4" t="n">
-        <v>55.72518062376687</v>
+        <v>9.055341851362117</v>
       </c>
       <c r="E4" t="n">
-        <v>33.88856900210827</v>
+        <v>5.506892462842593</v>
       </c>
       <c r="F4" t="n">
-        <v>20.66779025293812</v>
+        <v>3.358515916102444</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>104.3358399685502</v>
+        <v>16.9545739948894</v>
       </c>
       <c r="D5" t="n">
-        <v>104.3353159524171</v>
+        <v>16.95448884226777</v>
       </c>
       <c r="E5" t="n">
-        <v>33.88856900210827</v>
+        <v>5.506892462842593</v>
       </c>
       <c r="F5" t="n">
-        <v>20.66779025293812</v>
+        <v>3.358515916102444</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>93.94990601723735</v>
+        <v>15.26685972780107</v>
       </c>
       <c r="D6" t="n">
-        <v>93.94861990103271</v>
+        <v>15.26665073391782</v>
       </c>
       <c r="E6" t="n">
-        <v>33.88856900210827</v>
+        <v>5.506892462842593</v>
       </c>
       <c r="F6" t="n">
-        <v>20.66779025293812</v>
+        <v>3.358515916102444</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
